--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5518,14 +5518,14 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59903-2023</t>
+          <t>A 59939-2023</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -5572,123 +5572,123 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="S57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/artfynd/A 59939-2023 artfynd.xlsx", "A 59939-2023")</f>
+        <v/>
+      </c>
+      <c r="T57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/kartor/A 59939-2023 karta.png", "A 59939-2023")</f>
+        <v/>
+      </c>
+      <c r="V57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomål/A 59939-2023 FSC-klagomål.docx", "A 59939-2023")</f>
+        <v/>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomålsmail/A 59939-2023 FSC-klagomål mail.docx", "A 59939-2023")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsyn/A 59939-2023 tillsynsbegäran.docx", "A 59939-2023")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsynsmail/A 59939-2023 tillsynsbegäran mail.docx", "A 59939-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A 59903-2023</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>45254</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>VINDELN</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
           <t>Mörk kolflarnlav</t>
         </is>
       </c>
-      <c r="S57">
+      <c r="S58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/artfynd/A 59903-2023 artfynd.xlsx", "A 59903-2023")</f>
         <v/>
       </c>
-      <c r="T57">
+      <c r="T58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/kartor/A 59903-2023 karta.png", "A 59903-2023")</f>
         <v/>
       </c>
-      <c r="U57">
+      <c r="U58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/knärot/A 59903-2023 karta knärot.png", "A 59903-2023")</f>
         <v/>
       </c>
-      <c r="V57">
+      <c r="V58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomål/A 59903-2023 FSC-klagomål.docx", "A 59903-2023")</f>
         <v/>
       </c>
-      <c r="W57">
+      <c r="W58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomålsmail/A 59903-2023 FSC-klagomål mail.docx", "A 59903-2023")</f>
         <v/>
       </c>
-      <c r="X57">
+      <c r="X58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsyn/A 59903-2023 tillsynsbegäran.docx", "A 59903-2023")</f>
         <v/>
       </c>
-      <c r="Y57">
+      <c r="Y58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsynsmail/A 59903-2023 tillsynsbegäran mail.docx", "A 59903-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 59939-2023</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="n">
-        <v>45254</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>45258</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>VINDELN</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="S58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/artfynd/A 59939-2023 artfynd.xlsx", "A 59939-2023")</f>
-        <v/>
-      </c>
-      <c r="T58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/kartor/A 59939-2023 karta.png", "A 59939-2023")</f>
-        <v/>
-      </c>
-      <c r="V58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomål/A 59939-2023 FSC-klagomål.docx", "A 59939-2023")</f>
-        <v/>
-      </c>
-      <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomålsmail/A 59939-2023 FSC-klagomål mail.docx", "A 59939-2023")</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsyn/A 59939-2023 tillsynsbegäran.docx", "A 59939-2023")</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsynsmail/A 59939-2023 tillsynsbegäran mail.docx", "A 59939-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62833,14 +62833,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 53640-2023</t>
+          <t>A 53577-2023</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62858,7 +62858,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>15.5</v>
+        <v>4.7</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -62895,14 +62895,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 53577-2023</t>
+          <t>A 53640-2023</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62920,7 +62920,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63133,14 +63133,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 55427-2023</t>
+          <t>A 55426-2023</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63153,7 +63153,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -63190,14 +63190,14 @@
     <row r="1028" ht="15" customHeight="1">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 55426-2023</t>
+          <t>A 55431-2023</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63210,7 +63210,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -63247,14 +63247,14 @@
     <row r="1029" ht="15" customHeight="1">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>A 55431-2023</t>
+          <t>A 55427-2023</t>
         </is>
       </c>
       <c r="B1029" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63267,7 +63267,7 @@
         </is>
       </c>
       <c r="G1029" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -63304,14 +63304,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 55988-2023</t>
+          <t>A 56182-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -63361,14 +63361,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 56178-2023</t>
+          <t>A 55988-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63381,7 +63381,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -63418,14 +63418,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 56182-2023</t>
+          <t>A 56178-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         </is>
       </c>
       <c r="G1032" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -63475,14 +63475,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 57561-2023</t>
+          <t>A 56640-2023</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63532,14 +63532,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 56640-2023</t>
+          <t>A 57561-2023</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63879,14 +63879,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 57846-2023</t>
+          <t>A 57867-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63898,13 +63898,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1040" t="n">
-        <v>5.3</v>
+        <v>10.6</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -63941,14 +63936,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 57867-2023</t>
+          <t>A 57865-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63961,7 +63956,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>10.6</v>
+        <v>0.9</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -63998,14 +63993,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 57868-2023</t>
+          <t>A 57887-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64018,7 +64013,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64055,14 +64050,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 57865-2023</t>
+          <t>A 57846-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64074,8 +64069,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1043" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -64112,14 +64112,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 57887-2023</t>
+          <t>A 57868-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -64176,7 +64176,7 @@
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64283,14 +64283,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 58660-2023</t>
+          <t>A 58590-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64303,7 +64303,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -64340,14 +64340,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 58590-2023</t>
+          <t>A 58660-2023</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5518,14 +5518,14 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59939-2023</t>
+          <t>A 59903-2023</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>9.300000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -5572,123 +5572,123 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="S57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/artfynd/A 59903-2023 artfynd.xlsx", "A 59903-2023")</f>
+        <v/>
+      </c>
+      <c r="T57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/kartor/A 59903-2023 karta.png", "A 59903-2023")</f>
+        <v/>
+      </c>
+      <c r="U57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/knärot/A 59903-2023 karta knärot.png", "A 59903-2023")</f>
+        <v/>
+      </c>
+      <c r="V57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomål/A 59903-2023 FSC-klagomål.docx", "A 59903-2023")</f>
+        <v/>
+      </c>
+      <c r="W57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomålsmail/A 59903-2023 FSC-klagomål mail.docx", "A 59903-2023")</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsyn/A 59903-2023 tillsynsbegäran.docx", "A 59903-2023")</f>
+        <v/>
+      </c>
+      <c r="Y57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsynsmail/A 59903-2023 tillsynsbegäran mail.docx", "A 59903-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A 59939-2023</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>45254</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>VINDELN</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
           <t>Ullticka</t>
         </is>
       </c>
-      <c r="S57">
+      <c r="S58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/artfynd/A 59939-2023 artfynd.xlsx", "A 59939-2023")</f>
         <v/>
       </c>
-      <c r="T57">
+      <c r="T58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/kartor/A 59939-2023 karta.png", "A 59939-2023")</f>
         <v/>
       </c>
-      <c r="V57">
+      <c r="V58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomål/A 59939-2023 FSC-klagomål.docx", "A 59939-2023")</f>
         <v/>
       </c>
-      <c r="W57">
+      <c r="W58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomålsmail/A 59939-2023 FSC-klagomål mail.docx", "A 59939-2023")</f>
         <v/>
       </c>
-      <c r="X57">
+      <c r="X58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsyn/A 59939-2023 tillsynsbegäran.docx", "A 59939-2023")</f>
         <v/>
       </c>
-      <c r="Y57">
+      <c r="Y58">
         <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsynsmail/A 59939-2023 tillsynsbegäran mail.docx", "A 59939-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A 59903-2023</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="n">
-        <v>45254</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>VINDELN</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="S58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/artfynd/A 59903-2023 artfynd.xlsx", "A 59903-2023")</f>
-        <v/>
-      </c>
-      <c r="T58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/kartor/A 59903-2023 karta.png", "A 59903-2023")</f>
-        <v/>
-      </c>
-      <c r="U58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/knärot/A 59903-2023 karta knärot.png", "A 59903-2023")</f>
-        <v/>
-      </c>
-      <c r="V58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomål/A 59903-2023 FSC-klagomål.docx", "A 59903-2023")</f>
-        <v/>
-      </c>
-      <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/klagomålsmail/A 59903-2023 FSC-klagomål mail.docx", "A 59903-2023")</f>
-        <v/>
-      </c>
-      <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsyn/A 59903-2023 tillsynsbegäran.docx", "A 59903-2023")</f>
-        <v/>
-      </c>
-      <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2404/tillsynsmail/A 59903-2023 tillsynsbegäran mail.docx", "A 59903-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63304,14 +63304,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 56182-2023</t>
+          <t>A 56178-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -63361,14 +63361,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 55988-2023</t>
+          <t>A 56182-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63381,7 +63381,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -63418,14 +63418,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 56178-2023</t>
+          <t>A 55988-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         </is>
       </c>
       <c r="G1032" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -63482,7 +63482,7 @@
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63646,14 +63646,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 57816-2023</t>
+          <t>A 56943-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -63703,14 +63703,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 56943-2023</t>
+          <t>A 57819-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -63760,14 +63760,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 57819-2023</t>
+          <t>A 57816-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63879,14 +63879,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 57867-2023</t>
+          <t>A 57846-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63898,8 +63898,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1040" t="n">
-        <v>10.6</v>
+        <v>5.3</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -63936,14 +63941,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 57865-2023</t>
+          <t>A 57868-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63956,7 +63961,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -63993,14 +63998,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 57887-2023</t>
+          <t>A 57867-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64013,7 +64018,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>1.6</v>
+        <v>10.6</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64050,14 +64055,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 57846-2023</t>
+          <t>A 57865-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64069,13 +64074,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1043" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1043" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -64112,14 +64112,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 57868-2023</t>
+          <t>A 57887-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -64176,7 +64176,7 @@
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64290,7 +64290,7 @@
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64347,7 +64347,7 @@
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45254</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63304,14 +63304,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 55988-2023</t>
+          <t>A 56182-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -63361,14 +63361,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 56182-2023</t>
+          <t>A 55988-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63381,7 +63381,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -63425,7 +63425,7 @@
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63475,14 +63475,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 57561-2023</t>
+          <t>A 56640-2023</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63532,14 +63532,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 56640-2023</t>
+          <t>A 57561-2023</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63589,14 +63589,14 @@
     <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 56943-2023</t>
+          <t>A 56951-2023</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63609,7 +63609,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -63646,14 +63646,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 57819-2023</t>
+          <t>A 57816-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -63703,14 +63703,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 56951-2023</t>
+          <t>A 56943-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -63760,14 +63760,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 57816-2023</t>
+          <t>A 57819-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63879,14 +63879,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 57846-2023</t>
+          <t>A 57865-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63898,13 +63898,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1040" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -63941,14 +63936,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 57868-2023</t>
+          <t>A 57887-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63961,7 +63956,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -63998,14 +63993,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 57865-2023</t>
+          <t>A 57846-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64017,8 +64012,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1042" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64055,14 +64055,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 57887-2023</t>
+          <t>A 57868-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64075,7 +64075,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -64119,7 +64119,7 @@
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64176,7 +64176,7 @@
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64290,7 +64290,7 @@
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64347,7 +64347,7 @@
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64454,14 +64454,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 60810-2023</t>
+          <t>A 60859-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64473,8 +64473,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1050" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64511,14 +64516,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 60859-2023</t>
+          <t>A 60871-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64536,7 +64541,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64573,14 +64578,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 60871-2023</t>
+          <t>A 60810-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64592,13 +64597,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1052" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1052" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64635,14 +64635,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 61151-2023</t>
+          <t>A 61152-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64660,7 +64660,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64697,14 +64697,14 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 61152-2023</t>
+          <t>A 61151-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64722,7 +64722,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45254</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63304,14 +63304,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 56182-2023</t>
+          <t>A 56178-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -63361,14 +63361,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 55988-2023</t>
+          <t>A 56182-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63381,7 +63381,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -63418,14 +63418,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 56178-2023</t>
+          <t>A 55988-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         </is>
       </c>
       <c r="G1032" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -63482,7 +63482,7 @@
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63646,14 +63646,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 57816-2023</t>
+          <t>A 56943-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -63703,14 +63703,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 56943-2023</t>
+          <t>A 57819-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -63760,14 +63760,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 57819-2023</t>
+          <t>A 57816-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63879,14 +63879,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 57865-2023</t>
+          <t>A 57846-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63898,8 +63898,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1040" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -63936,14 +63941,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 57887-2023</t>
+          <t>A 57868-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63956,7 +63961,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -63993,14 +63998,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 57846-2023</t>
+          <t>A 57867-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64012,13 +64017,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1042" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1042" t="n">
-        <v>5.3</v>
+        <v>10.6</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64055,14 +64055,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 57868-2023</t>
+          <t>A 57865-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64075,7 +64075,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -64112,14 +64112,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 57867-2023</t>
+          <t>A 57887-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -64176,7 +64176,7 @@
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64283,14 +64283,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 58590-2023</t>
+          <t>A 58660-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64303,7 +64303,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -64340,14 +64340,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 58660-2023</t>
+          <t>A 58590-2023</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64454,14 +64454,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 60859-2023</t>
+          <t>A 60871-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64479,7 +64479,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64516,14 +64516,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 60871-2023</t>
+          <t>A 60810-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64535,13 +64535,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1051" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1051" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64578,14 +64573,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 60810-2023</t>
+          <t>A 60859-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64597,8 +64592,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1052" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64635,14 +64635,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 61152-2023</t>
+          <t>A 61151-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64660,7 +64660,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64697,14 +64697,14 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 61151-2023</t>
+          <t>A 61152-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64722,7 +64722,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45254</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63304,14 +63304,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 56178-2023</t>
+          <t>A 55988-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -63361,14 +63361,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 56182-2023</t>
+          <t>A 56178-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63381,7 +63381,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -63418,14 +63418,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 55988-2023</t>
+          <t>A 56182-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         </is>
       </c>
       <c r="G1032" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -63482,7 +63482,7 @@
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63703,14 +63703,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 57819-2023</t>
+          <t>A 57816-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -63760,14 +63760,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 57816-2023</t>
+          <t>A 57819-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63948,7 +63948,7 @@
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64119,7 +64119,7 @@
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64169,14 +64169,14 @@
     <row r="1045" ht="15" customHeight="1">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>A 58187-2023</t>
+          <t>A 58350-2023</t>
         </is>
       </c>
       <c r="B1045" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64189,7 +64189,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -64226,14 +64226,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 58350-2023</t>
+          <t>A 58187-2023</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64246,7 +64246,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -64283,14 +64283,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 58660-2023</t>
+          <t>A 58590-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64303,7 +64303,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -64340,14 +64340,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 58590-2023</t>
+          <t>A 58660-2023</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64454,14 +64454,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 60871-2023</t>
+          <t>A 60810-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64473,13 +64473,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1050" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1050" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64516,14 +64511,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 60810-2023</t>
+          <t>A 60859-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64535,8 +64530,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1051" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64573,14 +64573,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 60859-2023</t>
+          <t>A 60871-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64598,7 +64598,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64635,14 +64635,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 61151-2023</t>
+          <t>A 61152-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64660,7 +64660,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64697,14 +64697,14 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 61152-2023</t>
+          <t>A 61151-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64722,7 +64722,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45254</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63482,7 +63482,7 @@
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63589,14 +63589,14 @@
     <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 56951-2023</t>
+          <t>A 56943-2023</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63609,7 +63609,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -63646,14 +63646,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 56943-2023</t>
+          <t>A 56951-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -63710,7 +63710,7 @@
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63948,7 +63948,7 @@
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64005,7 +64005,7 @@
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64119,7 +64119,7 @@
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64176,7 +64176,7 @@
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64283,14 +64283,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 58590-2023</t>
+          <t>A 58660-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64303,7 +64303,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -64340,14 +64340,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 58660-2023</t>
+          <t>A 58590-2023</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64454,14 +64454,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 60810-2023</t>
+          <t>A 60871-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64473,8 +64473,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1050" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64511,14 +64516,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 60859-2023</t>
+          <t>A 60810-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64530,13 +64535,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1051" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1051" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64573,14 +64573,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 60871-2023</t>
+          <t>A 60859-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64598,7 +64598,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64635,14 +64635,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 61152-2023</t>
+          <t>A 61151-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64660,7 +64660,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64697,14 +64697,14 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 61151-2023</t>
+          <t>A 61152-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64722,7 +64722,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45254</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63133,14 +63133,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 55427-2023</t>
+          <t>A 55426-2023</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63153,7 +63153,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -63190,14 +63190,14 @@
     <row r="1028" ht="15" customHeight="1">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 55426-2023</t>
+          <t>A 55431-2023</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63210,7 +63210,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -63247,14 +63247,14 @@
     <row r="1029" ht="15" customHeight="1">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>A 55431-2023</t>
+          <t>A 55427-2023</t>
         </is>
       </c>
       <c r="B1029" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63267,7 +63267,7 @@
         </is>
       </c>
       <c r="G1029" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -63311,7 +63311,7 @@
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63482,7 +63482,7 @@
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63589,14 +63589,14 @@
     <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 56943-2023</t>
+          <t>A 56951-2023</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63609,7 +63609,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -63646,14 +63646,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 56951-2023</t>
+          <t>A 56943-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -63710,7 +63710,7 @@
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63879,14 +63879,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 57846-2023</t>
+          <t>A 57867-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63898,13 +63898,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1040" t="n">
-        <v>5.3</v>
+        <v>10.6</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -63941,14 +63936,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 57868-2023</t>
+          <t>A 57846-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63960,8 +63955,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1041" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -63998,14 +63998,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 57867-2023</t>
+          <t>A 57868-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64018,7 +64018,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>10.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64062,7 +64062,7 @@
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64119,7 +64119,7 @@
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64169,14 +64169,14 @@
     <row r="1045" ht="15" customHeight="1">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>A 58350-2023</t>
+          <t>A 58187-2023</t>
         </is>
       </c>
       <c r="B1045" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64189,7 +64189,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -64226,14 +64226,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 58187-2023</t>
+          <t>A 58350-2023</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64246,7 +64246,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -64283,14 +64283,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 58660-2023</t>
+          <t>A 58590-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64303,7 +64303,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -64340,14 +64340,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 58590-2023</t>
+          <t>A 58660-2023</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64454,14 +64454,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 60871-2023</t>
+          <t>A 60810-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64473,13 +64473,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1050" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G1050" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64516,14 +64511,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 60810-2023</t>
+          <t>A 60859-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64535,8 +64530,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G1051" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64573,14 +64573,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 60859-2023</t>
+          <t>A 60871-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64598,7 +64598,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64642,7 +64642,7 @@
         <v>45262</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64704,7 +64704,7 @@
         <v>45262</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1054"/>
+  <dimension ref="A1:Y1055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45254</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63304,14 +63304,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 55988-2023</t>
+          <t>A 56178-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -63361,14 +63361,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 56178-2023</t>
+          <t>A 55988-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63381,7 +63381,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -63425,7 +63425,7 @@
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63482,7 +63482,7 @@
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63589,14 +63589,14 @@
     <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 56951-2023</t>
+          <t>A 56943-2023</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63609,7 +63609,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -63646,14 +63646,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 56943-2023</t>
+          <t>A 56951-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -63710,7 +63710,7 @@
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63936,14 +63936,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 57846-2023</t>
+          <t>A 57865-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63955,13 +63955,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1041" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1041" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -63998,14 +63993,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 57868-2023</t>
+          <t>A 57887-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64018,7 +64013,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64055,14 +64050,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 57865-2023</t>
+          <t>A 57846-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64074,8 +64069,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1043" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -64112,14 +64112,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 57887-2023</t>
+          <t>A 57868-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -64176,7 +64176,7 @@
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64283,14 +64283,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 58590-2023</t>
+          <t>A 58660-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64303,7 +64303,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -64340,14 +64340,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 58660-2023</t>
+          <t>A 58590-2023</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64461,7 +64461,7 @@
         <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64511,14 +64511,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 60859-2023</t>
+          <t>A 60871-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64536,7 +64536,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64573,14 +64573,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 60871-2023</t>
+          <t>A 60859-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64598,7 +64598,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64635,14 +64635,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 61151-2023</t>
+          <t>A 61152-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64660,7 +64660,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64694,67 +64694,124 @@
       </c>
       <c r="R1053" s="2" t="inlineStr"/>
     </row>
-    <row r="1054">
+    <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 61152-2023</t>
+          <t>A 61151-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45262</v>
       </c>
       <c r="C1054" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>VINDELN</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G1054" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1054" s="2" t="inlineStr"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>A 62341-2023</t>
+        </is>
+      </c>
+      <c r="B1055" s="1" t="n">
         <v>45267</v>
       </c>
-      <c r="D1054" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="E1054" t="inlineStr">
-        <is>
-          <t>VINDELN</t>
-        </is>
-      </c>
-      <c r="F1054" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="G1054" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1054" s="2" t="inlineStr"/>
+      <c r="C1055" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>VINDELN</t>
+        </is>
+      </c>
+      <c r="G1055" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1055" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45254</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44628</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44638</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>44641</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>44641</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44641</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44641</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44641</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>44641</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>44644</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>44651</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>44652</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>44652</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44659</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44659</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>44659</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>44673</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>44673</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44680</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44684</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44685</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>44685</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44686</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>44689</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44689</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44689</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44691</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>44692</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44693</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44693</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44697</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44697</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44697</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44698</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>44711</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44714</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44714</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44715</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44715</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44716</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>44720</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44721</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44721</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44722</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44722</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>44722</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44730</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>44739</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44740</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>44742</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44742</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44743</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>44746</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44750</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44757</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44757</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44758</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>44771</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>44777</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>44783</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>44784</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>44788</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44791</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44794</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44797</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44797</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>44798</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44798</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44798</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44798</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44798</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44799</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44802</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44802</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44803</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44803</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44804</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44804</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44805</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44806</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44806</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>44809</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44809</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44810</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44812</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44813</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44816</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44817</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44817</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44817</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>44817</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44817</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>44818</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44818</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>44818</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>44819</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44820</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44820</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44820</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>44823</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>44824</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44825</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>44827</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44827</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>44832</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>44839</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44839</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44840</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44840</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44841</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44842</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>44842</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>44844</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>44844</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44845</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44845</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44845</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44846</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44848</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44848</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44851</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44854</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44855</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44855</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44855</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44859</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44859</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44859</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44860</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44860</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44861</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44861</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>44865</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44865</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44869</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44869</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>44869</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44871</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44871</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44872</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44872</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>44872</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>44872</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>44873</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44874</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44874</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44874</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>44874</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44874</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44874</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44875</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44875</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44876</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44879</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44880</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>44881</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44882</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>44886</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>44886</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44886</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>44886</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44888</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>44889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>44889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>44889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44890</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44890</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>44890</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44893</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44894</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>44902</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44902</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44902</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44902</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>44902</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>44902</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>44902</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>44902</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44902</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44902</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44904</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>44904</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44910</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>44910</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44910</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44910</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>44910</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44578,7 +44578,7 @@
         <v>44910</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44910</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>44910</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>44911</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>44911</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44914</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>44914</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44914</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>44915</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>44915</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44915</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>44916</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>44916</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44917</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44917</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44917</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>44917</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>44918</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>44923</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>44924</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         <v>44924</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>44924</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>44924</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44925</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44925</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>44925</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>44925</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44925</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44925</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44925</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>44925</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44925</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44925</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>44925</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44925</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>44925</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>44925</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>44925</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>44925</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44925</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>44925</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44927</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44931</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44935</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44935</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>44935</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>44938</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>44942</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44942</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44942</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44943</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44944</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>44944</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44949</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>44952</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44953</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>44953</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44953</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>44956</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44956</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>44956</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>44962</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>44962</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>44963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44965</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>44965</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44965</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44966</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44967</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44967</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>44970</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>44971</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>44971</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44973</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44974</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>44978</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49370,7 +49370,7 @@
         <v>44979</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44987</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>44988</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>44995</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>44998</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>44998</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44999</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45001</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45001</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45005</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45007</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45014</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45019</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45019</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45019</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>45019</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45019</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45019</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45019</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45019</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45019</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45021</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45028</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45028</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45033</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45040</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45043</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45043</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45056</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45057</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>45057</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45057</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45061</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45061</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45062</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45061</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45061</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45063</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45063</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45068</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45068</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45068</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45069</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45072</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>45072</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>45077</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45076</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45076</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45077</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45084</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45087</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45092</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45093</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45093</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45093</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45096</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45097</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45098</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45098</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45098</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>45098</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45098</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45099</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45099</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45104</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53639,7 +53639,7 @@
         <v>45103</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53696,7 +53696,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45104</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45104</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45104</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45105</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45106</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45113</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45114</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45114</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>45114</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45114</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45114</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45114</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45114</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45114</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45114</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45117</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45117</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45117</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54804,7 +54804,7 @@
         <v>45118</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54866,7 +54866,7 @@
         <v>45118</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>45118</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>45118</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45118</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45132</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>45132</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45132</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>45135</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45141</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45141</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45141</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45141</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45141</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55637,7 +55637,7 @@
         <v>45145</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45145</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45148</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45148</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45148</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45149</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45152</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45152</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>45151</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45152</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45152</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45153</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45153</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45153</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45154</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45154</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45156</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45155</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45155</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45157</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45159</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45159</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45159</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45159</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45159</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45159</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45159</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45159</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45161</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45162</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>45162</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45162</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45162</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45163</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45163</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45163</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>45163</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45163</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45163</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45166</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>45166</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45166</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45166</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45166</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45166</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>45166</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45166</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45166</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58682,7 +58682,7 @@
         <v>45167</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45168</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>45169</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45170</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58925,7 +58925,7 @@
         <v>45170</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45170</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45170</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45174</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45175</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45175</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45176</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45180</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45181</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45181</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45181</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45182</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45182</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>45183</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45187</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45187</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45187</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45188</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>45188</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45190</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45190</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45190</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45190</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45195</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45196</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>45197</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>45197</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>45201</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45201</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45204</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45204</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
         <v>45205</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>45205</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45208</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45208</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45208</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45208</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45210</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45210</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45211</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45213</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>45215</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>45215</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>45217</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45218</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45219</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45219</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45223</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45224</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>45224</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>45225</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45225</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45225</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45225</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45226</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>45226</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45226</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45226</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45229</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45230</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45230</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45231</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45231</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>45232</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45238</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45238</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63304,14 +63304,14 @@
     <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 56178-2023</t>
+          <t>A 55988-2023</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>
@@ -63361,14 +63361,14 @@
     <row r="1031" ht="15" customHeight="1">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>A 55988-2023</t>
+          <t>A 56178-2023</t>
         </is>
       </c>
       <c r="B1031" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63381,7 +63381,7 @@
         </is>
       </c>
       <c r="G1031" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -63425,7 +63425,7 @@
         <v>45240</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63482,7 +63482,7 @@
         <v>45243</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45243</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63646,14 +63646,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 56951-2023</t>
+          <t>A 57816-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -63703,14 +63703,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 57816-2023</t>
+          <t>A 57819-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63723,7 +63723,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -63760,14 +63760,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 57819-2023</t>
+          <t>A 56951-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -63824,7 +63824,7 @@
         <v>45245</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>45247</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -63936,14 +63936,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 57865-2023</t>
+          <t>A 57846-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -63955,8 +63955,13 @@
           <t>VINDELN</t>
         </is>
       </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1041" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -63993,14 +63998,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 57887-2023</t>
+          <t>A 57868-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64013,7 +64018,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64050,14 +64055,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 57846-2023</t>
+          <t>A 57865-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64069,13 +64074,8 @@
           <t>VINDELN</t>
         </is>
       </c>
-      <c r="F1043" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1043" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -64112,14 +64112,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 57868-2023</t>
+          <t>A 57887-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -64169,14 +64169,14 @@
     <row r="1045" ht="15" customHeight="1">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>A 58187-2023</t>
+          <t>A 58350-2023</t>
         </is>
       </c>
       <c r="B1045" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64189,7 +64189,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -64226,14 +64226,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 58350-2023</t>
+          <t>A 58187-2023</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64246,7 +64246,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -64290,7 +64290,7 @@
         <v>45251</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64347,7 +64347,7 @@
         <v>45251</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64404,7 +64404,7 @@
         <v>45254</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64461,7 +64461,7 @@
         <v>45260</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64511,14 +64511,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 60871-2023</t>
+          <t>A 60859-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64536,7 +64536,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64573,14 +64573,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 60859-2023</t>
+          <t>A 60871-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64598,7 +64598,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64642,7 +64642,7 @@
         <v>45262</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64704,7 +64704,7 @@
         <v>45262</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64766,7 +64766,7 @@
         <v>45267</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -564,7 +564,7 @@
         <v>44168</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         <v>44267</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44515</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>44432</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44532</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>44042</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44788</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44118</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44257</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44512</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44690</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>43878</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44137</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44497</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>45217</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45225</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>43563</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44131</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>44910</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44911</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44917</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>45041</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44074</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44463</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45148</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45152</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45159</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45224</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>43334</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>43441</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>43444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>43483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43647</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>43862</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>44096</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>44118</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44144</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>44163</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44257</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44439</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44496</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44742</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44917</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44924</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44966</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44979</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44987</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44991</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45159</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45170</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45190</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45210</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45225</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45254</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45254</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43315</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>43320</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>43327</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>43354</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>43354</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>43363</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>43364</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>43381</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>43395</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>43395</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43397</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43404</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43404</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43406</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>43406</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43420</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>43420</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>43425</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>43425</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>43425</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>43425</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>43425</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>43425</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43432</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>43433</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43446</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43446</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43453</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>43454</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>43454</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>43467</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>43467</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>43470</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>43472</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>43472</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>43476</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>43476</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>43476</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>43481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>43481</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>43482</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>43483</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>43488</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>43488</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>43488</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>43490</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>43495</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>43495</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>43508</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>43515</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>43516</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>43522</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>43522</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>43522</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>43525</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43526</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>43526</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>43530</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>43530</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43531</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43537</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43538</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43543</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43551</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>43558</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>43559</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>43567</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>43570</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>43572</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>43572</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43572</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>43572</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>43591</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>43591</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>43595</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>43597</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>43597</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>43598</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43598</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43602</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>43609</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>43609</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>43612</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>43619</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>43621</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>43630</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>43644</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>43647</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>43647</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43651</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43654</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43654</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43654</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43676</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>43686</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>43686</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>43690</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43693</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>43696</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>43704</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>43710</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>43710</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43710</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43710</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>43718</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>43719</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>43719</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>43719</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>43723</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43725</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>43738</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>43749</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>43749</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>43754</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43755</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>43759</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>43761</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>43762</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>43763</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>43768</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>43768</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>43770</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>43780</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>43782</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>43782</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>43783</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43783</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>43786</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>43796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43801</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43812</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43818</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43826</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43829</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43829</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43838</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>43839</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>43840</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>43840</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>43847</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>43847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>43847</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>43847</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>43847</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>43847</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>43852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>43860</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>43860</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>43861</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43864</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43864</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43864</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43864</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43878</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43894</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43906</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43910</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43917</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43917</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43917</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43921</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>43928</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>43936</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>43936</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>43936</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>43936</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>43942</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>43948</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>43948</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>43949</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>43950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>43964</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43965</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43971</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>43971</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43973</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>43976</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>43986</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44004</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44004</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44006</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44006</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>44014</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44014</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44022</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44049</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44053</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44055</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>44055</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>44060</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44061</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44061</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44064</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>44069</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44071</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44074</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44078</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44078</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44081</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44082</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44082</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>44082</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44082</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44082</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44082</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44082</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>44090</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>44090</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44095</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44097</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44098</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>44098</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>44098</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44102</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44102</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44105</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44106</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44106</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44109</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44109</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44118</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44118</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44118</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44123</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44123</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44123</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44124</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44124</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44124</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44125</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>44125</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44125</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44126</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44130</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44131</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44131</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44133</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44137</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44138</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>44146</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44146</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>44146</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44151</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44151</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44151</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>44153</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44153</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44154</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44158</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>44161</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44162</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>44165</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44166</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>44167</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44167</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44167</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>44167</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44167</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>44167</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44168</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44168</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44180</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44183</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44187</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44201</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44203</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44208</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44215</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44245</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44256</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44258</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44264</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>44270</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44281</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44281</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>44281</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44302</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44309</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>44319</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44323</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44323</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44334</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44340</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44340</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>44340</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>44340</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>44340</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44340</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44340</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44340</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44341</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44342</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44348</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44349</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44351</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44354</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44356</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44360</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44365</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44368</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44368</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44371</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44371</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44376</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44379</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44382</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44383</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44384</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44384</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44385</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44398</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44400</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44400</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44415</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44414</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>44418</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44419</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44419</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>44423</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>44426</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44426</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44426</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44432</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>44432</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44432</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44439</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44440</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44441</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44446</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44446</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44449</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44449</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44452</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44455</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44455</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44455</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>44455</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44455</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44459</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44462</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44462</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44462</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44463</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44473</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44473</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44479</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44483</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44484</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44488</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44488</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44489</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44490</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44491</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44494</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44494</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44494</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44500</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44502</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44505</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44508</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44509</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44509</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>44511</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>44511</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44522</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>44523</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44526</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44531</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44536</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44536</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>44536</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44536</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44537</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44540</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44540</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44544</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44544</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>44545</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44545</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44546</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44552</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44559</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44559</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44559</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44565</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>44565</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44572</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>44572</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44586</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44592</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44600</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44602</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>44608</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44610</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44614</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44627</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44627</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44628</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v